--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Severity %NoDispo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Severity RPM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Severity IPM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda No Convertida" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bajo Rendimiento" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin Conversión" sheetId="5" state="visible" r:id="rId5"/>
@@ -16,9 +16,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Destino" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por País" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de Acción" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · BajoRend" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · BajoRend" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · BajoRend" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sev ND" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sev IPM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · BajoRend" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sin Conv" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sev ND" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sev IPM" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · BajoRend" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sin Conv" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sev ND" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sev IPM" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · BajoRend" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sin Conv" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,9 +36,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
+    <numFmt numFmtId="166" formatCode="$0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -137,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +166,7 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -669,6 +680,312 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2C · Severity %NoDispo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2C · P80 · target &lt;3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>&gt;60%</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.004339739615623063</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>20-60%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.03502789832610043</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>5-20%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>950</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.1472411655300682</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>3-5%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>503</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.07796032238065716</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>&lt;3%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>4745</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.7354308741475512</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2C · Severity IPM (USD/M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2C · P80 · target ≥ $650</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5827</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.9031308121512709</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;$200</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.02045877247365158</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>$200-$650</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.02061376317420955</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>$650-$1500</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.02278363298202108</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.03301301921884687</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -708,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -810,7 +1127,7 @@
       <c r="I6" s="14" t="n">
         <v>0.04813673692601449</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="16" t="n">
         <v>346.8995050330905</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -860,7 +1177,7 @@
       <c r="I7" s="14" t="n">
         <v>0.02955366098691914</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="16" t="n">
         <v>-6.424450754981815</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -910,7 +1227,7 @@
       <c r="I8" s="14" t="n">
         <v>0.03995257885046238</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="16" t="n">
         <v>497.0889020710736</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -960,7 +1277,7 @@
       <c r="I9" s="14" t="n">
         <v>0.04159456152228139</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1010,7 +1327,7 @@
       <c r="I10" s="14" t="n">
         <v>0.1747304618355415</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1060,7 +1377,7 @@
       <c r="I11" s="14" t="n">
         <v>0.08305249837282032</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="16" t="n">
         <v>531.6908834848632</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1110,7 +1427,7 @@
       <c r="I12" s="14" t="n">
         <v>0.04998583953408435</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>-36.23626918924676</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1160,7 +1477,7 @@
       <c r="I13" s="14" t="n">
         <v>0.02653768980512077</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="16" t="n">
         <v>-743.6671641157939</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1210,7 +1527,7 @@
       <c r="I14" s="14" t="n">
         <v>0.0133118256822509</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="16" t="n">
         <v>-125.6743177491009</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1260,7 +1577,7 @@
       <c r="I15" s="14" t="n">
         <v>0.0416399699855067</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="16" t="n">
         <v>-293.6829085277479</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1310,7 +1627,7 @@
       <c r="I16" s="14" t="n">
         <v>0.07087493585869134</v>
       </c>
-      <c r="J16" s="15" t="n">
+      <c r="J16" s="16" t="n">
         <v>-467.6817705905702</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1360,7 +1677,7 @@
       <c r="I17" s="14" t="n">
         <v>0.3290496372545912</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="16" t="n">
         <v>-104.7652678551024</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1410,7 +1727,7 @@
       <c r="I18" s="14" t="n">
         <v>0.009929514697036027</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="16" t="n">
         <v>298.318494045913</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1460,7 +1777,7 @@
       <c r="I19" s="14" t="n">
         <v>0.04990980299639927</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J19" s="16" t="n">
         <v>153.7122163520694</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1510,7 +1827,7 @@
       <c r="I20" s="14" t="n">
         <v>0.04108139981306019</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="16" t="n">
         <v>-104.3720264178027</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1560,7 +1877,7 @@
       <c r="I21" s="14" t="n">
         <v>0.2681968485147567</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="16" t="n">
         <v>62.47291108993599</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1610,7 +1927,7 @@
       <c r="I22" s="14" t="n">
         <v>0.008423245777215567</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1660,7 +1977,7 @@
       <c r="I23" s="14" t="n">
         <v>0.03913569499977869</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J23" s="16" t="n">
         <v>68.27537365182884</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1710,7 +2027,7 @@
       <c r="I24" s="14" t="n">
         <v>0.009220515369527399</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="16" t="n">
         <v>648.4110317276271</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1760,7 +2077,7 @@
       <c r="I25" s="14" t="n">
         <v>0.09294892906544171</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="J25" s="16" t="n">
         <v>-864.7950489860559</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1810,7 +2127,7 @@
       <c r="I26" s="14" t="n">
         <v>0.01702873713722349</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1860,7 +2177,7 @@
       <c r="I27" s="14" t="n">
         <v>0.1169323124518128</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="J27" s="16" t="n">
         <v>298.6417879327149</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1910,7 +2227,7 @@
       <c r="I28" s="14" t="n">
         <v>0.04254958082851609</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J28" s="16" t="n">
         <v>-879.8111977046948</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1960,7 +2277,7 @@
       <c r="I29" s="14" t="n">
         <v>0.02741702159425875</v>
       </c>
-      <c r="J29" s="15" t="n">
+      <c r="J29" s="16" t="n">
         <v>32.61433174414544</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2010,7 +2327,7 @@
       <c r="I30" s="14" t="n">
         <v>0.1041393921622883</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="16" t="n">
         <v>263.6936940657562</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2060,7 +2377,7 @@
       <c r="I31" s="14" t="n">
         <v>0.01392220667294061</v>
       </c>
-      <c r="J31" s="15" t="n">
+      <c r="J31" s="16" t="n">
         <v>274.5821587377708</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2110,7 +2427,7 @@
       <c r="I32" s="14" t="n">
         <v>0.01247843410654324</v>
       </c>
-      <c r="J32" s="15" t="n">
+      <c r="J32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2160,7 +2477,7 @@
       <c r="I33" s="14" t="n">
         <v>0.02951829311355665</v>
       </c>
-      <c r="J33" s="15" t="n">
+      <c r="J33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2210,7 +2527,7 @@
       <c r="I34" s="14" t="n">
         <v>0.09474893963871513</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="16" t="n">
         <v>607.2141822545702</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2260,7 +2577,7 @@
       <c r="I35" s="14" t="n">
         <v>0.002936022892269046</v>
       </c>
-      <c r="J35" s="15" t="n">
+      <c r="J35" s="16" t="n">
         <v>285.6262083017709</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2310,7 +2627,7 @@
       <c r="I36" s="14" t="n">
         <v>0.01403716355614342</v>
       </c>
-      <c r="J36" s="15" t="n">
+      <c r="J36" s="16" t="n">
         <v>-139.093099508461</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2360,7 +2677,7 @@
       <c r="I37" s="14" t="n">
         <v>0.01700671721035248</v>
       </c>
-      <c r="J37" s="15" t="n">
+      <c r="J37" s="16" t="n">
         <v>325.7445975599683</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2410,7 +2727,7 @@
       <c r="I38" s="14" t="n">
         <v>0.048104978976165</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="J38" s="16" t="n">
         <v>512.2650021748794</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2460,7 +2777,7 @@
       <c r="I39" s="14" t="n">
         <v>0.01330246309966461</v>
       </c>
-      <c r="J39" s="15" t="n">
+      <c r="J39" s="16" t="n">
         <v>313.7393999982993</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2510,7 +2827,7 @@
       <c r="I40" s="14" t="n">
         <v>0.01881177026454356</v>
       </c>
-      <c r="J40" s="15" t="n">
+      <c r="J40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -2560,7 +2877,7 @@
       <c r="I41" s="14" t="n">
         <v>0.04380350750387037</v>
       </c>
-      <c r="J41" s="15" t="n">
+      <c r="J41" s="16" t="n">
         <v>514.2458769003863</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -2610,7 +2927,7 @@
       <c r="I42" s="14" t="n">
         <v>0.006403959034309993</v>
       </c>
-      <c r="J42" s="15" t="n">
+      <c r="J42" s="16" t="n">
         <v>574.5020507404769</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -2660,7 +2977,7 @@
       <c r="I43" s="14" t="n">
         <v>0.04362934552906532</v>
       </c>
-      <c r="J43" s="15" t="n">
+      <c r="J43" s="16" t="n">
         <v>240.8476656965516</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -2710,7 +3027,7 @@
       <c r="I44" s="14" t="n">
         <v>0.02378789466223753</v>
       </c>
-      <c r="J44" s="15" t="n">
+      <c r="J44" s="16" t="n">
         <v>230.5326669090775</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -2760,7 +3077,7 @@
       <c r="I45" s="14" t="n">
         <v>0.03168822323853115</v>
       </c>
-      <c r="J45" s="15" t="n">
+      <c r="J45" s="16" t="n">
         <v>78.4224370298128</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -2810,7 +3127,7 @@
       <c r="I46" s="14" t="n">
         <v>0.00198852081167804</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J46" s="16" t="n">
         <v>641.34817693818</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -2860,7 +3177,7 @@
       <c r="I47" s="14" t="n">
         <v>0.001850912172328737</v>
       </c>
-      <c r="J47" s="15" t="n">
+      <c r="J47" s="16" t="n">
         <v>607.4643384625845</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -2910,7 +3227,7 @@
       <c r="I48" s="14" t="n">
         <v>0.01516964896342646</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J48" s="16" t="n">
         <v>410.2401829187379</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -2960,7 +3277,7 @@
       <c r="I49" s="14" t="n">
         <v>0.001989302541573864</v>
       </c>
-      <c r="J49" s="15" t="n">
+      <c r="J49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -3010,7 +3327,7 @@
       <c r="I50" s="14" t="n">
         <v>0.002944862558084232</v>
       </c>
-      <c r="J50" s="15" t="n">
+      <c r="J50" s="16" t="n">
         <v>-118.8356802683925</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -3060,7 +3377,7 @@
       <c r="I51" s="14" t="n">
         <v>0.05161119428469778</v>
       </c>
-      <c r="J51" s="15" t="n">
+      <c r="J51" s="16" t="n">
         <v>-1422.255347383538</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -3110,7 +3427,7 @@
       <c r="I52" s="14" t="n">
         <v>0.000449579350103729</v>
       </c>
-      <c r="J52" s="15" t="n">
+      <c r="J52" s="16" t="n">
         <v>170.3970893320684</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -3160,7 +3477,7 @@
       <c r="I53" s="14" t="n">
         <v>0.06443471374058292</v>
       </c>
-      <c r="J53" s="15" t="n">
+      <c r="J53" s="16" t="n">
         <v>-647.7637926181919</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3210,7 +3527,7 @@
       <c r="I54" s="14" t="n">
         <v>0.149896846139529</v>
       </c>
-      <c r="J54" s="15" t="n">
+      <c r="J54" s="16" t="n">
         <v>633.6556836859613</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -3260,7 +3577,7 @@
       <c r="I55" s="14" t="n">
         <v>0.06789144203762386</v>
       </c>
-      <c r="J55" s="15" t="n">
+      <c r="J55" s="16" t="n">
         <v>408.2423930172558</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -3279,7 +3596,2356 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2C · Top 50 Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2C · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rk</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CorpName</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>PaisDestino</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Trafico</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>%NoDispo</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BandaNoDispo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham Garden Lake Buena Vista Disney Springs</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2334085</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.008461131449797243</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Chicago</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>2101643</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.07186520260577081</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Paris Las Vegas Resort &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Caesars Entertainment</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>1888758</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.01237268088341651</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Orlando Buena Vista Palace - Disney Springs® Area</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>1865509</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.05938647307517679</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Regency Miami</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>1557653</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0.05347532473535505</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Rio Hotel &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>1495188</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0.007102116924426896</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn Manhattan 6th Ave - Chelsea by IHG</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>1473689</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.02217224936876098</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Place Waikiki Beach</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Honolulu Area</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>1460071</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.00692089631257658</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Hard Rock Hotel &amp; Casino Punta Cana - All Inclusive</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>PAM Hotels</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>1451690</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.09842735019184537</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>New York-New York Hotel &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>MGM Resorts</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>1450731</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0.009246373035386987</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Presidente InterContinental Cancún</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Presidente Intercontinental</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>1445379</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.04616228684656412</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn New York City - Times Square by IHG</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>1407008</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.05195137483226819</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>The Grand Oasis Cancún</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>1307963</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.0452933301630092</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Park MGM Las Vegas</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>MGM Resorts</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>1264102</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0.03963050450042797</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Ramada by Wyndham Kissimmee Gateway</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>1238696</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.01517482901373703</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas Hilton at Resorts World</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>1227122</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.04093236043359992</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Grand Hyatt Barcelona</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1198435</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.1151026129911092</v>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Place San Juan</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>1183275</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.007982928735923602</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>TRYP by Wyndham New York City Times Square / Midtown</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>1155778</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.01131359136443158</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Centric The Loop Chicago</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>1125274</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.002620695048494855</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>DoubleTree by Hilton Montreal</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>1122336</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>0.09968761582984062</v>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Hilton New York Fashion District</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>1095185</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0.01252939001173318</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>SAHARA Las Vegas</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>1094844</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>0.04488127989010306</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>New York Hilton Midtown</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>1084872</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.0226054317928751</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Dream Midtown, by Hyatt</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>1077104</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0.5416236500839288</v>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>DoubleTree by Hilton Orlando Theme Park Resort</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>1074378</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.01894026124883421</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Hilton New York Times Square</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>1072991</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>0.02607757194608342</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Mandalay Bay Resort &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>MGM Resorts</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>1065975</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.1005792818780928</v>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn Express Nashville Downtown Conf Ctr, an IHG Hotel</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>1062658</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.03918382019426758</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Hotel NYX Cancun</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>1054407</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0.3243263749197416</v>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Grand Central New York</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>1047081</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.1368681124000913</v>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Grand Fiesta Americana Coral Beach - All Inclusive</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>GRUPO POSADAS</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>1020980</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.04983937001704245</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Best Western Plus Atlantic Beach Resort</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Best Western</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>1018106</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>0.01894596436913249</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Grand Hyatt Washington</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>1017835</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>0.01056949309072689</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Rosen Inn International</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>1015544</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>0.2050378910219547</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham Garden Chinatown</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>1000750</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>0.05451811141643767</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Regency New Orleans</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>990675</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>0.1086390592272945</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Homewood Suites New York/Midtown Manhattan Times Square</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>984955</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>0.006133275124244254</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>ARIA Resort &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>MGM Resorts</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>983358</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>0.02200012609853176</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Miami Airport Blue Lagoon</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>963050</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0.08894865271792742</v>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham Grand Pittsburgh Downtown</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Pittsburgh Area</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>950998</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0.01364461334303542</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>DoubleTree by Hilton New York Times Square West</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>932911</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.04876135022526264</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Hampton Inn Manhattan-Chelsea</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>916234</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.01458251931275198</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn Washington-Central/White House by IHG</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>899196</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0.02398364761409081</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Miami Downtown</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>895314</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>0.1175006757405782</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>The Royal Sands All Suites Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>882791</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>0.002630294146632668</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Regency Savannah</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Savannah Area</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>882783</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>0.01612287504403687</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham Grand Orlando Resort Bonnet Creek</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>878631</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>0.007980597087969808</v>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Flamingo Cancun All Inclusive</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>878483</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>0.04209415549304881</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Conrad Las Vegas at Resorts World</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>873395</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>0.03227520194184762</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2B Opaco · Severity %NoDispo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2B (OP) · P80 · target &lt;3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>&gt;60%</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.002361489554950046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>20-60%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.02125340599455041</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>5-20%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1630</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.098698153194066</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>3-5%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1193</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.0722373599757796</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>&lt;3%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>13302</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.805449591280654</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2B Opaco · Severity IPM (USD/M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2B (OP) · P80 · target ≥ $650</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11680</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.7072358462004239</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;$200</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1046</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.0633363608840448</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>$200-$650</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>985</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.05964274901604602</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>$650-$1500</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1249</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.07562821677263094</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1555</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.09415682712685437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3319,7 +5985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3421,7 +6087,7 @@
       <c r="I6" s="14" t="n">
         <v>0.007080392428480992</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="16" t="n">
         <v>204.7653020426888</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -3471,7 +6137,7 @@
       <c r="I7" s="14" t="n">
         <v>0.03810156285010617</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="16" t="n">
         <v>-760.4739053009391</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -3521,7 +6187,7 @@
       <c r="I8" s="14" t="n">
         <v>0.004458635198851902</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="16" t="n">
         <v>541.6052344105367</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -3571,7 +6237,7 @@
       <c r="I9" s="14" t="n">
         <v>0.02882027046729039</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="16" t="n">
         <v>385.3394353826405</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -3621,7 +6287,7 @@
       <c r="I10" s="14" t="n">
         <v>0.1037553460472873</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="16" t="n">
         <v>114.0583485010147</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -3671,7 +6337,7 @@
       <c r="I11" s="14" t="n">
         <v>0.002476662329619381</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="16" t="n">
         <v>55.0312589368742</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -3721,7 +6387,7 @@
       <c r="I12" s="14" t="n">
         <v>0.009755770738239102</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>69.62692274192977</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -3771,7 +6437,7 @@
       <c r="I13" s="14" t="n">
         <v>0.01091586830341802</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="16" t="n">
         <v>598.1433782937478</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -3821,7 +6487,7 @@
       <c r="I14" s="14" t="n">
         <v>0.006036237221910039</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="16" t="n">
         <v>450.9630940908036</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -3871,7 +6537,7 @@
       <c r="I15" s="14" t="n">
         <v>0.01715884766226278</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -3921,7 +6587,7 @@
       <c r="I16" s="14" t="n">
         <v>0.002872763182710784</v>
       </c>
-      <c r="J16" s="15" t="n">
+      <c r="J16" s="16" t="n">
         <v>40.91256795820612</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -3971,7 +6637,7 @@
       <c r="I17" s="14" t="n">
         <v>0.01800997263028225</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="16" t="n">
         <v>302.4372081994656</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -4021,7 +6687,7 @@
       <c r="I18" s="14" t="n">
         <v>0.01344577169790012</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="16" t="n">
         <v>13.41137293542669</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -4071,7 +6737,7 @@
       <c r="I19" s="14" t="n">
         <v>0.04493012423010238</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J19" s="16" t="n">
         <v>-217.7982497779363</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -4121,7 +6787,7 @@
       <c r="I20" s="14" t="n">
         <v>0.01929805562970835</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="16" t="n">
         <v>606.356517695096</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -4171,7 +6837,7 @@
       <c r="I21" s="14" t="n">
         <v>0.008669370941675688</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="16" t="n">
         <v>95.19909049351604</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -4221,7 +6887,7 @@
       <c r="I22" s="14" t="n">
         <v>0.02254025640954424</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="16" t="n">
         <v>101.6117946595695</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -4271,7 +6937,7 @@
       <c r="I23" s="14" t="n">
         <v>0.000774277901696027</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J23" s="16" t="n">
         <v>-74.08525527279994</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -4321,7 +6987,7 @@
       <c r="I24" s="14" t="n">
         <v>0.0288363765312982</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="16" t="n">
         <v>-744.3343870129813</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -4371,7 +7037,7 @@
       <c r="I25" s="14" t="n">
         <v>0.005367395898590611</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="J25" s="16" t="n">
         <v>278.838702566277</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -4421,7 +7087,7 @@
       <c r="I26" s="14" t="n">
         <v>0.01252065553066111</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="16" t="n">
         <v>323.2893058972699</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -4471,7 +7137,7 @@
       <c r="I27" s="14" t="n">
         <v>0.004681712188568799</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="J27" s="16" t="n">
         <v>551.0478058050313</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -4521,7 +7187,7 @@
       <c r="I28" s="14" t="n">
         <v>0.009216525363742888</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J28" s="16" t="n">
         <v>463.9008142269799</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -4571,7 +7237,7 @@
       <c r="I29" s="14" t="n">
         <v>0.0437410725745111</v>
       </c>
-      <c r="J29" s="15" t="n">
+      <c r="J29" s="16" t="n">
         <v>446.9432979012904</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -4621,7 +7287,7 @@
       <c r="I30" s="14" t="n">
         <v>0.005335825847137359</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="16" t="n">
         <v>649.3183090140146</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -4671,7 +7337,7 @@
       <c r="I31" s="14" t="n">
         <v>0.007429924365760854</v>
       </c>
-      <c r="J31" s="15" t="n">
+      <c r="J31" s="16" t="n">
         <v>-62.07961596784848</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -4721,7 +7387,7 @@
       <c r="I32" s="14" t="n">
         <v>0.002569320414516403</v>
       </c>
-      <c r="J32" s="15" t="n">
+      <c r="J32" s="16" t="n">
         <v>-144.0592829392164</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -4771,7 +7437,7 @@
       <c r="I33" s="14" t="n">
         <v>0.06911874664826172</v>
       </c>
-      <c r="J33" s="15" t="n">
+      <c r="J33" s="16" t="n">
         <v>28.54955825977389</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -4821,7 +7487,7 @@
       <c r="I34" s="14" t="n">
         <v>0.009001570332194167</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="16" t="n">
         <v>-96.03823635026799</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -4871,7 +7537,7 @@
       <c r="I35" s="14" t="n">
         <v>0.06592058730713668</v>
       </c>
-      <c r="J35" s="15" t="n">
+      <c r="J35" s="16" t="n">
         <v>243.7744733593215</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -4921,7 +7587,7 @@
       <c r="I36" s="14" t="n">
         <v>0.01772299347509232</v>
       </c>
-      <c r="J36" s="15" t="n">
+      <c r="J36" s="16" t="n">
         <v>444.0898882162394</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -4971,7 +7637,7 @@
       <c r="I37" s="14" t="n">
         <v>0.06893049871211965</v>
       </c>
-      <c r="J37" s="15" t="n">
+      <c r="J37" s="16" t="n">
         <v>53.89433091502028</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -5021,7 +7687,7 @@
       <c r="I38" s="14" t="n">
         <v>0.01376338186096557</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="J38" s="16" t="n">
         <v>-238.8407938821226</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -5071,7 +7737,7 @@
       <c r="I39" s="14" t="n">
         <v>0.01511466436710411</v>
       </c>
-      <c r="J39" s="15" t="n">
+      <c r="J39" s="16" t="n">
         <v>41.51003933142648</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -5121,7 +7787,7 @@
       <c r="I40" s="14" t="n">
         <v>0.09161952404020585</v>
       </c>
-      <c r="J40" s="15" t="n">
+      <c r="J40" s="16" t="n">
         <v>-1445.54139869183</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -5171,7 +7837,7 @@
       <c r="I41" s="14" t="n">
         <v>0.01642208843075016</v>
       </c>
-      <c r="J41" s="15" t="n">
+      <c r="J41" s="16" t="n">
         <v>313.454629855166</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -5221,7 +7887,7 @@
       <c r="I42" s="14" t="n">
         <v>0.002403249893732098</v>
       </c>
-      <c r="J42" s="15" t="n">
+      <c r="J42" s="16" t="n">
         <v>375.9902470252707</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -5271,7 +7937,7 @@
       <c r="I43" s="14" t="n">
         <v>0.03415882690271543</v>
       </c>
-      <c r="J43" s="15" t="n">
+      <c r="J43" s="16" t="n">
         <v>367.984560211274</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -5321,7 +7987,7 @@
       <c r="I44" s="14" t="n">
         <v>0.02709020127902782</v>
       </c>
-      <c r="J44" s="15" t="n">
+      <c r="J44" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -5371,7 +8037,7 @@
       <c r="I45" s="14" t="n">
         <v>0.04978947015710784</v>
       </c>
-      <c r="J45" s="15" t="n">
+      <c r="J45" s="16" t="n">
         <v>59.17367399442615</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -5421,7 +8087,7 @@
       <c r="I46" s="14" t="n">
         <v>0.02049333983015527</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J46" s="16" t="n">
         <v>10.19566509359849</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -5471,7 +8137,7 @@
       <c r="I47" s="14" t="n">
         <v>0.00420231163084198</v>
       </c>
-      <c r="J47" s="15" t="n">
+      <c r="J47" s="16" t="n">
         <v>-747.6110219154961</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -5521,7 +8187,7 @@
       <c r="I48" s="14" t="n">
         <v>0.006056278423057808</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J48" s="16" t="n">
         <v>51.44922673777148</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -5571,7 +8237,7 @@
       <c r="I49" s="14" t="n">
         <v>0.007080957360269403</v>
       </c>
-      <c r="J49" s="15" t="n">
+      <c r="J49" s="16" t="n">
         <v>1.488804272492142</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -5621,7 +8287,7 @@
       <c r="I50" s="14" t="n">
         <v>0.0319071523500317</v>
       </c>
-      <c r="J50" s="15" t="n">
+      <c r="J50" s="16" t="n">
         <v>306.9318640735319</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -5671,7 +8337,7 @@
       <c r="I51" s="14" t="n">
         <v>0.007306387101313574</v>
       </c>
-      <c r="J51" s="15" t="n">
+      <c r="J51" s="16" t="n">
         <v>-282.73788583212</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -5721,7 +8387,7 @@
       <c r="I52" s="14" t="n">
         <v>0.01014228511014694</v>
       </c>
-      <c r="J52" s="15" t="n">
+      <c r="J52" s="16" t="n">
         <v>479.8073698625584</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -5771,7 +8437,7 @@
       <c r="I53" s="14" t="n">
         <v>0.00530354746699539</v>
       </c>
-      <c r="J53" s="15" t="n">
+      <c r="J53" s="16" t="n">
         <v>-449.6637739714179</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -5821,7 +8487,7 @@
       <c r="I54" s="14" t="n">
         <v>0.05014504591837735</v>
       </c>
-      <c r="J54" s="15" t="n">
+      <c r="J54" s="16" t="n">
         <v>-431.3950861583672</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -5871,7 +8537,7 @@
       <c r="I55" s="14" t="n">
         <v>0.01062423246949832</v>
       </c>
-      <c r="J55" s="15" t="n">
+      <c r="J55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -5890,7 +8556,2509 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2B Opaco · Top 50 Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2B (OP) · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rk</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CorpName</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>PaisDestino</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Trafico</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>%NoDispo</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BandaNoDispo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>The Manhattan at Times Square Hotel</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>5294560</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.01611654226224653</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Barceló Maya Tropical</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Barcelo</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>5052599</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.0005223054511153567</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Barceló Maya Palace</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Barcelo</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>4652585</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.005304363058385822</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Grand Fiesta Americana Coral Beach - All Inclusive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>GRUPO POSADAS</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>4580633</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.008267198005166536</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Viva Azteca by Wyndham</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>4303104</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0.00714646915342971</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Presidente InterContinental Cancún</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Presidente Intercontinental</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>4160873</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0.005484185650463256</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn Resort Orlando - Lake Buena Vista by IHG</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>3988728</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.01939214707044451</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Hotel Emporio Ixtapa - with Optional All Inclusive</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Emporio</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Ixtapa / Zihuatanejo</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>3980166</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.01453758461330507</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Grand Hotel Orlando at Universal Blvd</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>3937372</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.02727047380841841</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Marquis Reforma</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>3783053</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0.0467889294704568</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>The Gallivant Times Square</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>3761747</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.02298612851954158</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>OYO Hotel and Casino Las Vegas</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Oyo Rooms</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>3703649</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.04697016374931857</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham Garden Chinatown</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>3692817</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.007198840343293479</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Fairmont Royal York</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>3634222</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0.06600587415958629</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Hotel Riu Plaza Guadalajara</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>RIU</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>3580004</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.01825305223122656</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Serenade Punta Cana Beach &amp; Spa Resort</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>3574133</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.03731814121074957</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Novotel Paris Gare De Lyon</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>3527772</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.02327247906043815</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn Express New York - Manhattan West Side by IHG</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>3479696</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.01118057439500462</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>SAHARA Las Vegas</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>3439738</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.04030132527535527</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Hotel Astor</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>3432736</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.006472096892974001</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Hotel52</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>3424867</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>0.002449730164704206</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Embassy Suites by Hilton Orlando International Dr Conv Ctr</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>3250809</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0.04087720933466099</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Capellan de Getsemani</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>3224081</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>0.0003287758589191773</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Azulik</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>3166714</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.230178664697854</v>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Dreams Sands Cancún Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>3087043</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0.006256796552558549</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Four Points by Sheraton Puntacana Village</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>3065772</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.01414553985097391</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Secrets Akumal Riviera Maya</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>2925966</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>0.01273152182903014</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>The Royal Sands All Suites Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>2908996</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.001993127525785529</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Movich Buró 51</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Hoteles Movich</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Barranquilla Area</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>2904449</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.0008132351437398281</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Hotel Indigo Los Angeles Downtown by IHG</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles (and vicinity), CA, US</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>2893117</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0.009587583219067877</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>ibis Styles Mexico Reforma</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>2864290</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.001059599412070705</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Atlanta</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>2853481</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.02700841533551476</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn Santo Domingo</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>2826018</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>0.006850982548589569</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Aloft Cancún</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2804134</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>0.0303462673324456</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>JOIA Rose Hall by Iberostar</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Iberostar</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>2756716</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>0.01444653711154867</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Ziva Cancún</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Playa Resorts</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>2718893</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>0.05795851473375378</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Lopesan Costa Bavaro Resort, Spa &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Bávaro Area</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>2718698</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>0.02962447465661872</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Ramada by Wyndham Kissimmee Gateway</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>2707919</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>0.01236115260463847</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn New York City - Wall Street by IHG</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>2683721</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>0.02010902027446221</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Treasure Island – TI Las Vegas Hotel</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>2567766</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0.2141974774960024</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Hilton San Diego Bayfront</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>2511443</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0.00677578587290255</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Delirio Hotel</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>2503499</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.001251049031775128</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Princess Family Club Bavaro - Todo Incluido</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>2478357</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.003769029239935974</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Garden Inn Chicago OHare Airport</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>2440389</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0.01319707636774301</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Hampton Inn Madison Square Garden Area Hotel</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>2439728</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>0.03374843425168707</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Nobu Hotel Miami Beach</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>2420960</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>0.01062140638424427</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Hotel Porto Allegro Puerto Vallarta</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>2413548</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>0.003224298833087222</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Avani Cancun Airport</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>2411287</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>0.06947368770287403</v>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Kimpton Hotel Palomar Los Angeles Beverly Hills by IHG</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles (and vicinity), CA, US</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>2384126</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>0.007173278593497156</v>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Garden Inn Mexico City Polanco</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>2383865</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>0.0002273618682265984</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta CUG · Severity %NoDispo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CUG (UOP) · P80 · target &lt;3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>&gt;60%</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.001343784994400896</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>20-60%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>396</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.01773796192609182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>5-20%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.08371780515117581</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>3-5%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1429</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.06400895856662935</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>&lt;3%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>18601</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.8331914893617022</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta CUG · Severity IPM (USD/M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CUG (UOP) · P80 · target ≥ $650</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>17865</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.8002239641657335</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;$200</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.04756998880179171</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>$200-$650</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>427</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.01912653975363942</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>$650-$1500</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.03762597984322508</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2131</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.09545352743561031</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Severity · IPM (Income Per Million USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P80 · 18692 hoteles · target ≥ $650</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11954</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.63952493045153</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;$200</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1706</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.09126899208217419</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>$200-$650</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1732</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.09265996148084742</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>$650-$1500</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1684</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.09009201797560454</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1616</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.08645409800984379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5930,7 +11098,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6032,7 +11200,7 @@
       <c r="I6" s="14" t="n">
         <v>0.005784213013209309</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="16" t="n">
         <v>-815.6840989980536</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -6082,7 +11250,7 @@
       <c r="I7" s="14" t="n">
         <v>0.00226948086506127</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="16" t="n">
         <v>336.3152418033563</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -6132,7 +11300,7 @@
       <c r="I8" s="14" t="n">
         <v>0.09407428117251154</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="16" t="n">
         <v>-424.1892292326012</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -6182,7 +11350,7 @@
       <c r="I9" s="14" t="n">
         <v>0.01027767780363369</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="16" t="n">
         <v>-813.0517084589115</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -6232,7 +11400,7 @@
       <c r="I10" s="14" t="n">
         <v>0.03124109504822978</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="16" t="n">
         <v>-3421.649887026313</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -6282,7 +11450,7 @@
       <c r="I11" s="14" t="n">
         <v>0.09780718672349498</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="16" t="n">
         <v>29.93817041491827</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -6332,7 +11500,7 @@
       <c r="I12" s="14" t="n">
         <v>0.03372309667800081</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>-1078.080859168198</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -6382,7 +11550,7 @@
       <c r="I13" s="14" t="n">
         <v>0.06700920669688762</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -6432,7 +11600,7 @@
       <c r="I14" s="14" t="n">
         <v>0.1511592593898871</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="16" t="n">
         <v>-713.7959092967661</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -6482,7 +11650,7 @@
       <c r="I15" s="14" t="n">
         <v>0.008200905206147592</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="16" t="n">
         <v>179.5994684233308</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -6532,7 +11700,7 @@
       <c r="I16" s="14" t="n">
         <v>0.02122696151664523</v>
       </c>
-      <c r="J16" s="15" t="n">
+      <c r="J16" s="16" t="n">
         <v>-713.3041998545989</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -6582,7 +11750,7 @@
       <c r="I17" s="14" t="n">
         <v>0.001627281247601508</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="16" t="n">
         <v>-1262.559090740388</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -6632,7 +11800,7 @@
       <c r="I18" s="14" t="n">
         <v>0.02673035320853122</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="16" t="n">
         <v>147.2926629026014</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -6682,7 +11850,7 @@
       <c r="I19" s="14" t="n">
         <v>0.03082534176698633</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J19" s="16" t="n">
         <v>88.93228787127993</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -6732,7 +11900,7 @@
       <c r="I20" s="14" t="n">
         <v>0.315564543629338</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="16" t="n">
         <v>293.7410304149852</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -6782,7 +11950,7 @@
       <c r="I21" s="14" t="n">
         <v>0.1197295911477005</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="16" t="n">
         <v>-488.7554729391683</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -6832,7 +12000,7 @@
       <c r="I22" s="14" t="n">
         <v>0.03905730671454677</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="16" t="n">
         <v>-4132.899169648977</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -6882,7 +12050,7 @@
       <c r="I23" s="14" t="n">
         <v>0.2551093076715465</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J23" s="16" t="n">
         <v>-693.7951958603617</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -6932,7 +12100,7 @@
       <c r="I24" s="14" t="n">
         <v>0.02400452846223347</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="16" t="n">
         <v>-1433.890419772383</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -6982,7 +12150,7 @@
       <c r="I25" s="14" t="n">
         <v>0.03350867974208332</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="J25" s="16" t="n">
         <v>538.7529474700605</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -7032,7 +12200,7 @@
       <c r="I26" s="14" t="n">
         <v>0.05020019690998095</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="16" t="n">
         <v>508.938918156996</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -7082,7 +12250,7 @@
       <c r="I27" s="14" t="n">
         <v>0.06619899013383777</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="J27" s="16" t="n">
         <v>158.5244244095017</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -7132,7 +12300,7 @@
       <c r="I28" s="14" t="n">
         <v>0.1229153743736606</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J28" s="16" t="n">
         <v>63.76922497202855</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -7182,7 +12350,7 @@
       <c r="I29" s="14" t="n">
         <v>0.1893944082877206</v>
       </c>
-      <c r="J29" s="15" t="n">
+      <c r="J29" s="16" t="n">
         <v>585.2173043108961</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -7232,7 +12400,7 @@
       <c r="I30" s="14" t="n">
         <v>0.0321491184259477</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="16" t="n">
         <v>-106.2159681426815</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -7282,7 +12450,7 @@
       <c r="I31" s="14" t="n">
         <v>0.05619884768098958</v>
       </c>
-      <c r="J31" s="15" t="n">
+      <c r="J31" s="16" t="n">
         <v>267.5990826934193</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -7332,7 +12500,7 @@
       <c r="I32" s="14" t="n">
         <v>0.04798990742499561</v>
       </c>
-      <c r="J32" s="15" t="n">
+      <c r="J32" s="16" t="n">
         <v>-1193.846014161622</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -7382,7 +12550,7 @@
       <c r="I33" s="14" t="n">
         <v>0.004471737680488874</v>
       </c>
-      <c r="J33" s="15" t="n">
+      <c r="J33" s="16" t="n">
         <v>-446.4406962979877</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -7432,7 +12600,7 @@
       <c r="I34" s="14" t="n">
         <v>0.144364395213341</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -7482,7 +12650,7 @@
       <c r="I35" s="14" t="n">
         <v>0.05314780737603583</v>
       </c>
-      <c r="J35" s="15" t="n">
+      <c r="J35" s="16" t="n">
         <v>270.1675852771973</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -7532,7 +12700,7 @@
       <c r="I36" s="14" t="n">
         <v>0.04092556107624056</v>
       </c>
-      <c r="J36" s="15" t="n">
+      <c r="J36" s="16" t="n">
         <v>-1030.421384809308</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -7582,7 +12750,7 @@
       <c r="I37" s="14" t="n">
         <v>0.02823648398661607</v>
       </c>
-      <c r="J37" s="15" t="n">
+      <c r="J37" s="16" t="n">
         <v>405.6985124832175</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -7632,7 +12800,7 @@
       <c r="I38" s="14" t="n">
         <v>0.006502633720432467</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="J38" s="16" t="n">
         <v>-791.8824721478973</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -7682,7 +12850,7 @@
       <c r="I39" s="14" t="n">
         <v>0.2923963269642647</v>
       </c>
-      <c r="J39" s="15" t="n">
+      <c r="J39" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -7732,7 +12900,7 @@
       <c r="I40" s="14" t="n">
         <v>0.02984675899927653</v>
       </c>
-      <c r="J40" s="15" t="n">
+      <c r="J40" s="16" t="n">
         <v>-3162.573678474253</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -7782,7 +12950,7 @@
       <c r="I41" s="14" t="n">
         <v>0.03924821239887486</v>
       </c>
-      <c r="J41" s="15" t="n">
+      <c r="J41" s="16" t="n">
         <v>473.3694199126507</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -7832,7 +13000,7 @@
       <c r="I42" s="14" t="n">
         <v>0.0280415504270623</v>
       </c>
-      <c r="J42" s="15" t="n">
+      <c r="J42" s="16" t="n">
         <v>638.2328254909582</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -7882,7 +13050,7 @@
       <c r="I43" s="14" t="n">
         <v>0.02685809621054369</v>
       </c>
-      <c r="J43" s="15" t="n">
+      <c r="J43" s="16" t="n">
         <v>504.5550650171094</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -7932,7 +13100,7 @@
       <c r="I44" s="14" t="n">
         <v>0.3919601236662269</v>
       </c>
-      <c r="J44" s="15" t="n">
+      <c r="J44" s="16" t="n">
         <v>-4620.182984805399</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -7982,7 +13150,7 @@
       <c r="I45" s="14" t="n">
         <v>0.004760649238855672</v>
       </c>
-      <c r="J45" s="15" t="n">
+      <c r="J45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -8032,7 +13200,7 @@
       <c r="I46" s="14" t="n">
         <v>0.08122482232154511</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J46" s="16" t="n">
         <v>321.8331825485774</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -8082,7 +13250,7 @@
       <c r="I47" s="14" t="n">
         <v>0.01181267029696135</v>
       </c>
-      <c r="J47" s="15" t="n">
+      <c r="J47" s="16" t="n">
         <v>491.3260501843347</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -8132,7 +13300,7 @@
       <c r="I48" s="14" t="n">
         <v>0.08158339214919015</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J48" s="16" t="n">
         <v>-2797.297211812092</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -8182,7 +13350,7 @@
       <c r="I49" s="14" t="n">
         <v>0.003487099586370634</v>
       </c>
-      <c r="J49" s="15" t="n">
+      <c r="J49" s="16" t="n">
         <v>-543.689856240836</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -8232,7 +13400,7 @@
       <c r="I50" s="14" t="n">
         <v>0.01116012131157945</v>
       </c>
-      <c r="J50" s="15" t="n">
+      <c r="J50" s="16" t="n">
         <v>249.2780691693603</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -8282,7 +13450,7 @@
       <c r="I51" s="14" t="n">
         <v>0.009855321379327856</v>
       </c>
-      <c r="J51" s="15" t="n">
+      <c r="J51" s="16" t="n">
         <v>166.2019969086501</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -8332,7 +13500,7 @@
       <c r="I52" s="14" t="n">
         <v>0.008421650834228425</v>
       </c>
-      <c r="J52" s="15" t="n">
+      <c r="J52" s="16" t="n">
         <v>439.4317259941532</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -8382,7 +13550,7 @@
       <c r="I53" s="14" t="n">
         <v>0.005010488043630261</v>
       </c>
-      <c r="J53" s="15" t="n">
+      <c r="J53" s="16" t="n">
         <v>324.975527898196</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -8432,7 +13600,7 @@
       <c r="I54" s="14" t="n">
         <v>0.02611080052429775</v>
       </c>
-      <c r="J54" s="15" t="n">
+      <c r="J54" s="16" t="n">
         <v>647.525622627131</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -8482,7 +13650,7 @@
       <c r="I55" s="14" t="n">
         <v>0.04319346803742991</v>
       </c>
-      <c r="J55" s="15" t="n">
+      <c r="J55" s="16" t="n">
         <v>218.9005683730682</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -8501,152 +13669,2042 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Severity · RPM (GBM USD/M)</t>
+          <t>Canasta CUG · Top 50 Sin Conversión</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P80 · 18692 hoteles · target ≥ $650</t>
+          <t>CUG (UOP) · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Banda</t>
+          <t>Rk</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Rango</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Hoteles</t>
+          <t>CorpName</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>PaisDestino</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Trafico</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>%NoDispo</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BandaNoDispo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
+      <c r="A6" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>BKGS=0</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>11954</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0.63952493045153</v>
+          <t>Ocean El Faro</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Ocean by H10</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>3753136</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.026313728039698</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Caribe Deluxe Princess</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>3746115</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.02600080349909173</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Presidente InterContinental Cancún</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Presidente Intercontinental</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>3620612</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.006674838397486391</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Lopesan Costa Bavaro Resort, Spa &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Bávaro Area</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>3514903</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.01370649488762563</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Cancun, an All Inclusive Resort</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>3468224</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0.009249690908084368</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>DoubleTree by Hilton New York Downtown</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>3227336</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0.02539184020504837</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>The Manhattan at Times Square Hotel</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>2671081</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.01526909891538295</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana Princess Adults Only - All Inclusive</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>2637235</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.04476241214757123</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Cancun Bay All Inclusive Hotel</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>2630709</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.01994785436169489</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>The Royal Sands All Suites Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>2626647</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0.01013383222031739</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Dreams Macao Beach Punta Cana</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>2611182</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.01012721441860429</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Garden Inn New York Times Square South</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>2603425</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.1058885890701672</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Millennium Hilton New York One UN Plaza</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>2594163</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.02083870597182983</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Garden Inn New York/Central Park South-Midtown West</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>2573746</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0.028683483140916</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Garden Inn Orlando at SeaWorld</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>2521697</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.01070231673353301</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Aloft Cancún</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>2484634</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.01924871027282087</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Hilton San Francisco Union Square</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>2447285</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.03199545618920559</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Breathless Punta Cana Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>2399918</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.004892250485224912</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Miami Airport Blue Lagoon</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>2398837</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.05771838603456593</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Avani Cancun Airport</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>2324961</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.01089222571905507</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Hotel Marina El Cid Spa and Beach Resort Riviera Maya</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>2318332</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>0.0160718999694608</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Los Angeles/Universal City</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles (and vicinity), CA, US</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>2317985</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0.05173890253819589</v>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Canopy by Hilton Cancun La Isla</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>2293936</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>0.003601669793751875</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Whala!Urban Punta Cana</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>2272989</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.05465094639701292</v>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Distrikt Hotel New York City, Tapestry Collection by Hilton</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>2268132</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0.02083697068777302</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Motto by Hilton New York City Chelsea</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>2246789</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.04484221704841888</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>SLS Cancun Hotel</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>2241713</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>0.01140913221273196</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Dreams Riviera Cancun Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>2233821</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.005814252798232267</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Hacienda Real del Caribe</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>2204944</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.04201285837644856</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>EVEN Hotel Brooklyn by IHG</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>2161629</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0.02045031779273872</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Garden Inn New York/Manhattan-Midtown East</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>2151219</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.02877159415196686</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Orlando</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>2135769</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.1234103500893589</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Park Central Hotel New York</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>2130803</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>0.3565275626137189</v>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>&lt;$200</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1706</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0.09126899208217419</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Embassy Suites by Hilton Orlando Lake Buena Vista Resort</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2126012</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>0.01994955813984117</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Signia by Hilton Orlando - An Official Walt Disney World® Hotel</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>2072132</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>0.05408584009126832</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>$200-$650</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>1732</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0.09265996148084742</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Dreams Playa Mujeres Golf &amp; Spa Resort</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>2064559</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>0.002106987497087756</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn New York City - Wall Street by IHG</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>2037167</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>0.03635146259486827</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>$650-$1500</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>1684</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0.09009201797560454</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>1616</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.08645409800984379</v>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Hilton Garden Inn New York/West 35th Street</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>2032436</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>0.01368997596972303</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>whala!bavaro - All Inclusive</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Bávaro Area</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>2021572</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>0.01277718527957451</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Comfort Inn Cancún Aeropuerto</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>CHOICE</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>2018910</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0.004104194837808521</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Secrets Akumal Riviera Maya</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>2010065</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0.01116282309278556</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Park Royal Beach Cancun</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Park Royal</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>2003610</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.005201611091978978</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>NIZUC Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Las Brisas</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>1983235</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.006758654420681361</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Quality Hotel Nova Domus</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>CHOICE</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Rome Area</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>1981917</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0.335046321314162</v>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Embassy Suites by Hilton Orlando Lake Buena Vista South</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>1971201</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>0.02897421419733451</v>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Washington Hilton</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>1958265</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>0.06444326993537647</v>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Regency New Orleans</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>1930090</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>0.04735167790103052</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Holiday Inn &amp; Suites Orlando SW - Celebration Area by IHG</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Estados Unidos de América</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>1928664</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>0.03330958632504159</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Riu Palace Bavaro - All Inclusive</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>RIU</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>1905626</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>0.1853280759183596</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Majestic Elegance Punta Cana - All Inclusive</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>1900210</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>0.007822293325474553</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8694,7 +15752,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11204,7 +18262,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13556,7 +20614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15445,7 +22503,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17444,7 +24502,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19443,7 +26501,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21439,7 +28497,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17767,7 +17767,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17920,7 +17920,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20842,7 +20842,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22887,7 +22887,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25240,7 +25240,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -27083,7 +27083,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28926,7 +28926,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -34964,7 +34964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -35117,7 +35117,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -35278,7 +35278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37886,7 +37886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -39932,7 +39932,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42442,7 +42442,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44795,7 +44795,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -46638,7 +46638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48481,7 +48481,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -54526,7 +54526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56878,7 +56878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -58767,7 +58767,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60766,7 +60766,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -62765,7 +62765,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64761,7 +64761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:58 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
@@ -20,23 +20,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sev IPM" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · BajoRend" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sin Conv" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Demanda NC" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Demanda No Convertida" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Por Corp" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Por Destino" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Por País" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sev ND" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sev IPM" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · BajoRend" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sin Conv" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Demanda NC" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Por Corp" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Por Destino" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Por País" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · Sev ND" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · Sev IPM" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · BajoRend" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · Sin Conv" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · Demanda No Convertida" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · Por Corp" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · Por Destino" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta OP · Por País" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sev ND" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sev IPM" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · BajoRend" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sin Conv" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Demanda NC" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Demanda No Convertida" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Por Corp" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Por Destino" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Por País" sheetId="33" state="visible" r:id="rId33"/>
@@ -563,14 +563,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P80 · 18692 hoteles · target &lt;3%</t>
+          <t>P80 · 20016 hoteles · target &lt;3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.001658463513802696</v>
+        <v>0.001598721023181455</v>
       </c>
     </row>
     <row r="7">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02193451744061631</v>
+        <v>0.02058353317346123</v>
       </c>
     </row>
     <row r="8">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2034</v>
+        <v>2070</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1088166060346672</v>
+        <v>0.1034172661870504</v>
       </c>
     </row>
     <row r="9">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1404</v>
+        <v>1520</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07511234752835437</v>
+        <v>0.0759392486011191</v>
       </c>
     </row>
     <row r="10">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14813</v>
+        <v>15982</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7924780654825594</v>
+        <v>0.7984612310151878</v>
       </c>
     </row>
   </sheetData>
@@ -703,7 +703,7 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -723,7 +723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.004339739615623063</v>
+        <v>0.004296455424274973</v>
       </c>
     </row>
     <row r="7">
@@ -782,7 +782,7 @@
         <v>226</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.03502789832610043</v>
+        <v>0.03467853306736228</v>
       </c>
     </row>
     <row r="8">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1472411655300682</v>
+        <v>0.1489949363203928</v>
       </c>
     </row>
     <row r="9">
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07796032238065716</v>
+        <v>0.07764308731011202</v>
       </c>
     </row>
     <row r="10">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4745</v>
+        <v>4786</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7354308741475512</v>
+        <v>0.7343869878778579</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +876,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5827</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.9031308121512709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>132</v>
+        <v>6002</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02045877247365158</v>
+        <v>0.9209759091606567</v>
       </c>
     </row>
     <row r="8">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.02061376317420955</v>
+        <v>0.02056160810188737</v>
       </c>
     </row>
     <row r="9">
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.02278363298202108</v>
+        <v>0.02301672548718735</v>
       </c>
     </row>
     <row r="10">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.03301301921884687</v>
+        <v>0.03544575725026853</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1037,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8043,7 +8043,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
         <v>-114.2499999999998</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.06641728789635476</v>
+        <v>0.06641728789635475</v>
       </c>
       <c r="G25" s="16" t="n">
         <v>-15.35269129654919</v>
@@ -8918,7 +8918,7 @@
         <v>2278.94</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.06553750358113819</v>
+        <v>0.0655375035811382</v>
       </c>
       <c r="G29" s="16" t="n">
         <v>451.5186205317004</v>
@@ -9058,7 +9058,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.03071649846331387</v>
+        <v>0.03071649846331388</v>
       </c>
       <c r="G33" s="16" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9886,7 +9886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
         <v>6065.59</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.02500874661662356</v>
+        <v>0.02500874661662357</v>
       </c>
       <c r="G32" s="16" t="n">
         <v>422.1475259654633</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
         <v>5002.38</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.02768542912647766</v>
+        <v>0.02768542912647765</v>
       </c>
       <c r="G51" s="16" t="n">
         <v>596.7443993851685</v>
@@ -11698,7 +11698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11709,7 +11709,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11729,7 +11729,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.08471755571495086</v>
+        <v>0.08471755571495088</v>
       </c>
       <c r="G42" s="16" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13316,7 +13316,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13421,7 +13421,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13841,7 +13841,7 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13981,7 +13981,7 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.09765795669215852</v>
+        <v>0.0976579566921585</v>
       </c>
       <c r="G69" s="16" t="n">
         <v>0</v>
@@ -14016,7 +14016,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14156,7 +14156,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14471,7 +14471,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14996,7 +14996,7 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15136,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15941,7 +15941,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16046,7 +16046,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16641,7 +16641,7 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16781,7 +16781,7 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16816,7 +16816,7 @@
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16851,7 +16851,7 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16921,7 +16921,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17096,7 +17096,7 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17236,7 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17306,7 +17306,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C173" s="12" t="n">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C174" s="12" t="n">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,42 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17747,27 +17782,27 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Severity %NoDispo</t>
+          <t>Canasta OP · Severity %NoDispo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · P80 · target &lt;3%</t>
+          <t>B2B Opaco · P80 · target &lt;3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17808,7 +17843,7 @@
         <v>39</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.002361489554950046</v>
+        <v>0.002217925386715196</v>
       </c>
     </row>
     <row r="7">
@@ -17823,10 +17858,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02125340599455041</v>
+        <v>0.02007506824385805</v>
       </c>
     </row>
     <row r="8">
@@ -17841,10 +17876,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.098698153194066</v>
+        <v>0.09298225659690627</v>
       </c>
     </row>
     <row r="9">
@@ -17859,10 +17894,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1193</v>
+        <v>1214</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.0722373599757796</v>
+        <v>0.06904003639672429</v>
       </c>
     </row>
     <row r="10">
@@ -17877,10 +17912,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13302</v>
+        <v>14343</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.805449591280654</v>
+        <v>0.8156847133757962</v>
       </c>
     </row>
   </sheetData>
@@ -17906,21 +17941,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Severity IPM (USD/M)</t>
+          <t>Canasta OP · Severity IPM (USD/M)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · P80 · target ≥ $650</t>
+          <t>B2B Opaco · P80 · target ≥ $650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17958,10 +17993,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11680</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.7072358462004239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -17976,10 +18011,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1046</v>
+        <v>13736</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.0633363608840448</v>
+        <v>0.781164695177434</v>
       </c>
     </row>
     <row r="8">
@@ -17994,10 +18029,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>985</v>
+        <v>1002</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.05964274901604602</v>
+        <v>0.05698362147406733</v>
       </c>
     </row>
     <row r="9">
@@ -18012,10 +18047,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1249</v>
+        <v>1287</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07562821677263094</v>
+        <v>0.07319153776160145</v>
       </c>
     </row>
     <row r="10">
@@ -18030,10 +18065,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.09415682712685437</v>
+        <v>0.08866014558689718</v>
       </c>
     </row>
   </sheetData>
@@ -18066,14 +18101,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P80 · 18692 hoteles · target ≥ $650</t>
+          <t>P80 · 20016 hoteles · target ≥ $650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18111,10 +18146,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11954</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.63952493045153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -18129,10 +18164,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1706</v>
+        <v>14712</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.09126899208217419</v>
+        <v>0.7350119904076738</v>
       </c>
     </row>
     <row r="8">
@@ -18147,10 +18182,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1732</v>
+        <v>1824</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.09265996148084742</v>
+        <v>0.09112709832134293</v>
       </c>
     </row>
     <row r="9">
@@ -18165,10 +18200,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1684</v>
+        <v>1834</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.09009201797560454</v>
+        <v>0.09162669864108713</v>
       </c>
     </row>
     <row r="10">
@@ -18183,10 +18218,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1616</v>
+        <v>1646</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.08645409800984379</v>
+        <v>0.08223421262989608</v>
       </c>
     </row>
   </sheetData>
@@ -18220,21 +18255,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Top 50 Bajo Rendimiento</t>
+          <t>Canasta OP · Top 50 Bajo Rendimiento</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · BKGS&gt;0 · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · BKGS&gt;0 · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20828,21 +20863,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Top 50 Sin Conversión</t>
+          <t>Canasta OP · Top 50 Sin Conversión</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
+          <t>B2B Opaco · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22873,21 +22908,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Top 50 Demanda No Convertida</t>
+          <t>Canasta OP · Top 50 Demanda No Convertida</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
+          <t>B2B Opaco · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25252,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -25226,21 +25261,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Por Corporativo</t>
+          <t>Canasta OP · Por Corporativo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · Top 50 corp · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · Top 50 corp · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -26255,7 +26290,7 @@
         <v>6650.84</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.01545218050279508</v>
+        <v>0.01545218050279509</v>
       </c>
       <c r="G33" s="16" t="n">
         <v>377.3979118628988</v>
@@ -26360,7 +26395,7 @@
         <v>1208.42</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.1170824743635684</v>
+        <v>0.1170824743635683</v>
       </c>
       <c r="G36" s="16" t="n">
         <v>88.56938116870511</v>
@@ -26955,7 +26990,7 @@
         <v>2530.29</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.004535477776961692</v>
+        <v>0.004535477776961693</v>
       </c>
       <c r="G53" s="16" t="n">
         <v>432.1950086343691</v>
@@ -27069,21 +27104,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Por Destino</t>
+          <t>Canasta OP · Por Destino</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · Top 50 destinos · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · Top 50 destinos · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28895,7 +28930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -28906,27 +28941,27 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Por País</t>
+          <t>Canasta OP · Por País</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · todos los países · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · todos los países · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -30023,7 +30058,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -30688,7 +30723,7 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -30758,7 +30793,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -30793,7 +30828,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30898,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -30898,7 +30933,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -30933,7 +30968,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31108,7 +31143,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31213,7 +31248,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31283,7 +31318,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31388,7 +31423,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31528,7 +31563,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31563,7 +31598,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31598,7 +31633,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31633,7 +31668,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31668,7 +31703,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31703,7 +31738,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31738,7 +31773,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31808,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31808,7 +31843,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31843,7 +31878,7 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31878,7 +31913,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31948,7 +31983,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -31983,7 +32018,7 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32123,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32123,7 +32158,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32158,7 +32193,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32193,7 +32228,7 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32263,7 +32298,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32298,7 +32333,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32333,7 +32368,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32368,7 +32403,7 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32426,7 +32461,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.02242348302729265</v>
+        <v>0.02242348302729266</v>
       </c>
       <c r="G104" s="16" t="n">
         <v>0</v>
@@ -32543,7 +32578,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32578,7 +32613,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32613,7 +32648,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32718,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32718,7 +32753,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32788,7 +32823,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32823,7 +32858,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32858,7 +32893,7 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32893,7 +32928,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32928,7 +32963,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32963,7 +32998,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -32998,7 +33033,7 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33068,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33103,7 +33138,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33173,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33173,7 +33208,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33208,7 +33243,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33243,7 +33278,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33278,7 +33313,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33301,7 +33336,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="14" t="n">
-        <v>0.0839205103859544</v>
+        <v>0.08392051038595441</v>
       </c>
       <c r="G129" s="16" t="n">
         <v>0</v>
@@ -33313,7 +33348,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33348,7 +33383,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33418,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33418,7 +33453,7 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33453,7 +33488,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33488,7 +33523,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33523,7 +33558,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33558,7 +33593,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33628,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33628,7 +33663,7 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33663,7 +33698,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33698,7 +33733,7 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33768,7 +33803,7 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33803,7 +33838,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33838,7 +33873,7 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33873,7 +33908,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33908,7 +33943,7 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33943,7 +33978,7 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -33978,7 +34013,7 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34083,7 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34083,7 +34118,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34118,7 +34153,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34153,7 +34188,7 @@
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34188,7 +34223,7 @@
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34223,7 +34258,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34293,7 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34293,7 +34328,7 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34328,7 +34363,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34363,7 +34398,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34398,7 +34433,7 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34468,7 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34468,7 +34503,7 @@
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34538,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34538,7 +34573,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34573,7 +34608,7 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34608,7 +34643,7 @@
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34643,7 +34678,7 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34678,7 +34713,7 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34713,7 +34748,7 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34748,7 +34783,7 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34783,7 +34818,7 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34818,7 +34853,7 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34853,7 +34888,7 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34888,7 +34923,7 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34958,42 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -34957,14 +35027,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · P80 · target &lt;3%</t>
+          <t>CUG · P80 · target &lt;3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -35002,10 +35072,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.001343784994400896</v>
+        <v>0.001275142939410144</v>
       </c>
     </row>
     <row r="7">
@@ -35020,10 +35090,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01773796192609182</v>
+        <v>0.01641232363950475</v>
       </c>
     </row>
     <row r="8">
@@ -35038,10 +35108,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1869</v>
+        <v>2013</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.08371780515117581</v>
+        <v>0.08280202377524577</v>
       </c>
     </row>
     <row r="9">
@@ -35056,10 +35126,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1429</v>
+        <v>1487</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06400895856662935</v>
+        <v>0.06116572744848011</v>
       </c>
     </row>
     <row r="10">
@@ -35074,10 +35144,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18601</v>
+        <v>20381</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8331914893617022</v>
+        <v>0.8383447821973592</v>
       </c>
     </row>
   </sheetData>
@@ -35110,14 +35180,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · P80 · target ≥ $650</t>
+          <t>CUG · P80 · target ≥ $650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -35155,10 +35225,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>17865</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.8002239641657335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -35173,10 +35243,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1062</v>
+        <v>20673</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.04756998880179171</v>
+        <v>0.8503558060137386</v>
       </c>
     </row>
     <row r="8">
@@ -35191,10 +35261,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>427</v>
+        <v>473</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.01912653975363942</v>
+        <v>0.01945621323680638</v>
       </c>
     </row>
     <row r="9">
@@ -35209,10 +35279,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>840</v>
+        <v>978</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.03762597984322508</v>
+        <v>0.04022870305622969</v>
       </c>
     </row>
     <row r="10">
@@ -35227,10 +35297,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2131</v>
+        <v>2187</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.09545352743561031</v>
+        <v>0.08995927769322529</v>
       </c>
     </row>
   </sheetData>
@@ -35271,14 +35341,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · BKGS&gt;0 · ordenado por tráfico ↓</t>
+          <t>CUG · BKGS&gt;0 · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37879,14 +37949,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
+          <t>CUG · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -39932,7 +40002,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40224,7 +40294,7 @@
         <v>-5251.93</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>0.2646688483495444</v>
+        <v>0.2646688483495443</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>-1121.798096292656</v>
@@ -40619,7 +40689,7 @@
         </is>
       </c>
       <c r="L18" s="12" t="n">
-        <v>995439.9999999999</v>
+        <v>995440</v>
       </c>
     </row>
     <row r="19">
@@ -40704,7 +40774,7 @@
         <v>12183.57</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0.3076506690627428</v>
+        <v>0.3076506690627427</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>4033.634895483983</v>
@@ -40715,7 +40785,7 @@
         </is>
       </c>
       <c r="L20" s="12" t="n">
-        <v>929257.0000000002</v>
+        <v>929257.0000000001</v>
       </c>
     </row>
     <row r="21">
@@ -40848,7 +40918,7 @@
         <v>16661.96</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0.2043977109253355</v>
+        <v>0.2043977109253356</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>4112.800907573081</v>
@@ -40859,7 +40929,7 @@
         </is>
       </c>
       <c r="L23" s="12" t="n">
-        <v>828065</v>
+        <v>828065.0000000001</v>
       </c>
     </row>
     <row r="24">
@@ -41099,7 +41169,7 @@
         </is>
       </c>
       <c r="L28" s="12" t="n">
-        <v>744701.9999999999</v>
+        <v>744702</v>
       </c>
     </row>
     <row r="29">
@@ -41147,7 +41217,7 @@
         </is>
       </c>
       <c r="L29" s="12" t="n">
-        <v>729191.9999999999</v>
+        <v>729192</v>
       </c>
     </row>
     <row r="30">
@@ -42435,14 +42505,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
+          <t>CUG · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44775,7 +44845,7 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44788,14 +44858,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · Top 50 corp · ordenado por tráfico ↓</t>
+          <t>CUG · Top 50 corp · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45985,7 +46055,7 @@
         <v>22972.57</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.0138060554370632</v>
+        <v>0.01380605543706321</v>
       </c>
       <c r="G38" s="16" t="n">
         <v>2492.107671741196</v>
@@ -46020,7 +46090,7 @@
         <v>-3917.62</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.01237220616210537</v>
+        <v>0.01237220616210536</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>-448.1121473391075</v>
@@ -46207,7 +46277,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -46631,14 +46701,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · Top 50 destinos · ordenado por tráfico ↓</t>
+          <t>CUG · Top 50 destinos · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47058,7 +47128,7 @@
         <v>132249.45</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.05027503091966413</v>
+        <v>0.05027503091966414</v>
       </c>
       <c r="G16" s="16" t="n">
         <v>1597.05849704831</v>
@@ -47863,7 +47933,7 @@
         <v>71302.23999999999</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.05482390586902029</v>
+        <v>0.05482390586902028</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>2342.447665269028</v>
@@ -48450,7 +48520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -48461,7 +48531,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -48474,14 +48544,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · todos los países · ordenado por tráfico ↓</t>
+          <t>CUG · todos los países · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50033,7 +50103,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50208,7 +50278,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50278,7 +50348,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50313,7 +50383,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50348,7 +50418,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50453,7 +50523,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50593,7 +50663,7 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50663,7 +50733,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50791,7 +50861,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.02394806509505192</v>
+        <v>0.02394806509505193</v>
       </c>
       <c r="G70" s="16" t="n">
         <v>0</v>
@@ -50803,7 +50873,7 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50838,7 +50908,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -50896,7 +50966,7 @@
         <v>-404.21</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.02363224965867728</v>
+        <v>0.02363224965867727</v>
       </c>
       <c r="G73" s="16" t="n">
         <v>-484.9422090838634</v>
@@ -51048,7 +51118,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51188,7 +51258,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51223,7 +51293,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51258,7 +51328,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51328,7 +51398,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51363,7 +51433,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51433,7 +51503,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51503,7 +51573,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51573,7 +51643,7 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51631,7 +51701,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>0.005989277370389877</v>
+        <v>0.005989277370389876</v>
       </c>
       <c r="G94" s="16" t="n">
         <v>0</v>
@@ -51643,7 +51713,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51818,7 +51888,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51888,7 +51958,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -51981,7 +52051,7 @@
         <v>621.1</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.09683485707672723</v>
+        <v>0.09683485707672725</v>
       </c>
       <c r="G104" s="16" t="n">
         <v>1996.618189767131</v>
@@ -52028,7 +52098,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52133,7 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52098,7 +52168,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52133,7 +52203,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52168,7 +52238,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52203,7 +52273,7 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52238,7 +52308,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52273,7 +52343,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52308,7 +52378,7 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52343,7 +52413,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52378,7 +52448,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52448,7 +52518,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52483,7 +52553,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52518,7 +52588,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52553,7 +52623,7 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52623,7 +52693,7 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52658,7 +52728,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52693,7 +52763,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52728,7 +52798,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52763,7 +52833,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52798,7 +52868,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52833,7 +52903,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52868,7 +52938,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52903,7 +52973,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52938,7 +53008,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -52973,7 +53043,7 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53008,7 +53078,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53043,7 +53113,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53066,7 +53136,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>0.1979078506381394</v>
+        <v>0.1979078506381395</v>
       </c>
       <c r="G135" s="16" t="n">
         <v>0</v>
@@ -53078,7 +53148,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53113,7 +53183,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53148,7 +53218,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53183,7 +53253,7 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53218,7 +53288,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53253,7 +53323,7 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53288,7 +53358,7 @@
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53323,7 +53393,7 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53358,7 +53428,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53393,7 +53463,7 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53428,7 +53498,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53463,7 +53533,7 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53498,7 +53568,7 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53533,7 +53603,7 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53568,7 +53638,7 @@
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53603,7 +53673,7 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53638,7 +53708,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53673,7 +53743,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53743,7 +53813,7 @@
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53778,7 +53848,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53813,7 +53883,7 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53848,7 +53918,7 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53883,7 +53953,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53918,7 +53988,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -53953,7 +54023,7 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54023,7 +54093,7 @@
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54058,7 +54128,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54093,7 +54163,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54128,7 +54198,7 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54163,7 +54233,7 @@
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54198,7 +54268,7 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54233,7 +54303,7 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54268,7 +54338,7 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54303,7 +54373,7 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54338,7 +54408,7 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54373,7 +54443,7 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54408,7 +54478,7 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54443,7 +54513,7 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54478,7 +54548,42 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -54526,7 +54631,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -55116,7 +55221,7 @@
         <v>209.55</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>0.004610105137645561</v>
+        <v>0.004610105137645562</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>26.04884677758798</v>
@@ -55701,7 +55806,7 @@
         <v>-3503.83</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0.006016334148688283</v>
+        <v>0.006016334148688285</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>-507.7366944505629</v>
@@ -55881,7 +55986,7 @@
         <v>387.7699999999999</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>0.05205869796401383</v>
+        <v>0.05205869796401384</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>57.56178053340948</v>
@@ -56878,7 +56983,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57204,7 +57309,7 @@
         <v>5844174</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0.03571539793305264</v>
+        <v>0.03571539793305265</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -57888,7 +57993,7 @@
         <v>4221754</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0.06443080293167247</v>
+        <v>0.06443080293167248</v>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
@@ -58767,7 +58872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -58947,7 +59052,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5846</v>
+        <v>5845</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>1421356242</v>
@@ -59567,7 +59672,7 @@
         <v>143476.81</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>0.05172460609139643</v>
+        <v>0.05172460609139642</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>3172.531764939799</v>
@@ -60593,7 +60698,7 @@
         <v>15590.47</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0.01534950778724655</v>
+        <v>0.01534950778724654</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>1154.584160797399</v>
@@ -60766,7 +60871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -62765,7 +62870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -62831,7 +62936,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>30008</v>
+        <v>30007</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>10040023613</v>
@@ -64761,7 +64866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64825,7 +64930,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Escalar 31 hoteles Súper Críticos del P80 (%NoDispo &gt;60%)</t>
+          <t>Escalar 32 hoteles Súper Críticos del P80 (%NoDispo &gt;60%)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -64899,12 +65004,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Plan saneamiento 441 hoteles Crítica/Súper Crítica</t>
+          <t>Plan saneamiento 444 hoteles Crítica/Súper Crítica</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>220 migrados a Revisar</t>
+          <t>222 migrados a Revisar</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">

--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_7d.xlsx
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1037,7 +1037,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>0.02955366098691914</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-6.424450754981815</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>0.04998583953408435</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-36.23626918924676</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>0.02653768980512077</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>-743.6671641157939</v>
+        <v>0</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>0.0133118256822509</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>-125.6743177491009</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>0.0416399699855067</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>-293.6829085277479</v>
+        <v>0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>0.07087493585869134</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>-467.6817705905702</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>0.3290496372545912</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>-104.7652678551024</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>0.04108139981306019</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>-104.3720264178027</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>0.09294892906544171</v>
       </c>
       <c r="J25" s="16" t="n">
-        <v>-864.7950489860559</v>
+        <v>0</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>0.04254958082851609</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>-879.8111977046948</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>0.01403716355614342</v>
       </c>
       <c r="J36" s="16" t="n">
-        <v>-139.093099508461</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>0.002944862558084232</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>-118.8356802683925</v>
+        <v>0</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>0.05161119428469778</v>
       </c>
       <c r="J51" s="16" t="n">
-        <v>-1422.255347383538</v>
+        <v>0</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>0.06443471374058292</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>-647.7637926181919</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -5690,7 +5690,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-104.7652678551024</v>
+        <v>0</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>-1814.070816329226</v>
+        <v>0</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="16" t="n">
-        <v>-2014.484614937743</v>
+        <v>0</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -8043,7 +8043,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
         <v>0.06641728789635475</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>-15.35269129654919</v>
+        <v>0</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>0.01377003600613635</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>-1151.290282680609</v>
+        <v>0</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>0.004224830336804105</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>-41.99281311349937</v>
+        <v>0</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>0.05474299307727622</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>-301.9203439167827</v>
+        <v>0</v>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
@@ -9886,7 +9886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
         <v>0.1175984375521412</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>-134.0207498668855</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>0.02932297119156628</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>-75.18990681139714</v>
+        <v>0</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>0.0844021675568204</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>-41.73107731588496</v>
+        <v>0</v>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -11729,7 +11729,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
         <v>0.1037674954494018</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>-68.93633420202207</v>
+        <v>0</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>0.04783271122436374</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>-16.81672371014326</v>
+        <v>0</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>0.1646204858673438</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>-242.607220459823</v>
+        <v>0</v>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17955,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18247,7 +18247,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
@@ -18269,7 +18269,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18422,7 @@
         <v>0.03810156285010617</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-760.4739053009391</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>0.04493012423010238</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>-217.7982497779363</v>
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>0.000774277901696027</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>-74.08525527279994</v>
+        <v>0</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>0.0288363765312982</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>-744.3343870129813</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>0.007429924365760854</v>
       </c>
       <c r="J31" s="16" t="n">
-        <v>-62.07961596784848</v>
+        <v>0</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>0.002569320414516403</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>-144.0592829392164</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>0.009001570332194167</v>
       </c>
       <c r="J34" s="16" t="n">
-        <v>-96.03823635026799</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>0.01376338186096557</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>-238.8407938821226</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>0.09161952404020585</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>-1445.54139869183</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>0.00420231163084198</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-747.6110219154961</v>
+        <v>0</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>0.007306387101313574</v>
       </c>
       <c r="J51" s="16" t="n">
-        <v>-282.73788583212</v>
+        <v>0</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>0.00530354746699539</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>-449.6637739714179</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>0.05014504591837735</v>
       </c>
       <c r="J54" s="16" t="n">
-        <v>-431.3950861583672</v>
+        <v>0</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22901,7 +22901,7 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -22922,7 +22922,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23065,7 +23065,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-859.5199346387466</v>
+        <v>0</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-762.1488953438106</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>5</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>-2305.296374975763</v>
+        <v>0</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>16</v>
       </c>
       <c r="J25" s="16" t="n">
-        <v>-6372.064675536319</v>
+        <v>0</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>5</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>-3245.428400464913</v>
+        <v>0</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>2</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>-1425.454278746539</v>
+        <v>0</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>3</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>-1445.54139869183</v>
+        <v>0</v>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="16" t="n">
-        <v>-503.020870219243</v>
+        <v>0</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -25275,7 +25275,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25768,7 +25768,7 @@
         <v>0.160994037932987</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>-346.0339140392449</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>0.006590028254454681</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>-212.4751646870261</v>
+        <v>0</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>0.02586231017404018</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>-838.472418187805</v>
+        <v>0</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>0.007898327532920395</v>
       </c>
       <c r="G50" s="16" t="n">
-        <v>-835.351585064459</v>
+        <v>0</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28939,7 +28939,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -28961,7 +28961,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29734,7 +29734,7 @@
         <v>0.05909604243638321</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>-112.9392255476317</v>
+        <v>0</v>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>0.04619098092631751</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>-292.867202307351</v>
+        <v>0</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>0.3144020289619772</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>-149.3786458437206</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>0.1280315232155698</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>-87.52710690951095</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>0.02328213335434506</v>
       </c>
       <c r="G50" s="16" t="n">
-        <v>-164.6868441191261</v>
+        <v>0</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>0.1104616363622615</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>-6061.394849947678</v>
+        <v>0</v>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>0.06511139609118707</v>
       </c>
       <c r="G58" s="16" t="n">
-        <v>-356.5936036713294</v>
+        <v>0</v>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>0.01500835107253971</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>-3453.59751105289</v>
+        <v>0</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>0.05148135708001245</v>
       </c>
       <c r="G73" s="16" t="n">
-        <v>-9513.865752482074</v>
+        <v>0</v>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>0.1216154367725167</v>
       </c>
       <c r="G75" s="16" t="n">
-        <v>-1826.449316306927</v>
+        <v>0</v>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>0.001823187974400953</v>
       </c>
       <c r="G106" s="16" t="n">
-        <v>-12451.13360123034</v>
+        <v>0</v>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -35187,7 +35187,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
@@ -35348,7 +35348,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -35451,7 +35451,7 @@
         <v>0.005784213013209309</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-815.6840989980536</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>0.09407428117251154</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-424.1892292326012</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>0.01027767780363369</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-813.0517084589115</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>0.03124109504822978</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>-3421.649887026313</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>0.03372309667800081</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-1078.080859168198</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>0.1511592593898871</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>-713.7959092967661</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>0.02122696151664523</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>-713.3041998545989</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>0.001627281247601508</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>-1262.559090740388</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>0.1197295911477005</v>
       </c>
       <c r="J21" s="16" t="n">
-        <v>-488.7554729391683</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>0.03905730671454677</v>
       </c>
       <c r="J22" s="16" t="n">
-        <v>-4132.899169648977</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>0.2551093076715465</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>-693.7951958603617</v>
+        <v>0</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>0.02400452846223347</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>-1433.890419772383</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>0.0321491184259477</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>-106.2159681426815</v>
+        <v>0</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>0.04798990742499561</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>-1193.846014161622</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>0.004471737680488874</v>
       </c>
       <c r="J33" s="16" t="n">
-        <v>-446.4406962979877</v>
+        <v>0</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>0.04092556107624056</v>
       </c>
       <c r="J36" s="16" t="n">
-        <v>-1030.421384809308</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>0.006502633720432467</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>-791.8824721478973</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>0.02984675899927653</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>-3162.573678474253</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>0.3919601236662269</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>-4620.182984805399</v>
+        <v>0</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>0.08158339214919015</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-2797.297211812092</v>
+        <v>0</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>0.003487099586370634</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-543.689856240836</v>
+        <v>0</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -39980,7 +39980,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
@@ -40002,7 +40002,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40201,7 +40201,7 @@
         <v>0.3596064492746908</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>-1256.848653737828</v>
+        <v>0</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>0.3490366677995544</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-188.6610525785783</v>
+        <v>0</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>0.2646688483495443</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>-1121.798096292656</v>
+        <v>0</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>0.2287370749908211</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-1111.846539188752</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>0.2643447911819574</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-275.6571783812897</v>
+        <v>0</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>0.115702313966239</v>
       </c>
       <c r="J22" s="15" t="n">
-        <v>-149.7168365959892</v>
+        <v>0</v>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>0.3356761604068306</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>-963.3685466850559</v>
+        <v>0</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>0.08727681266949168</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>-201.5028323776119</v>
+        <v>0</v>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>0.1727792763117006</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>-1266.680754266678</v>
+        <v>0</v>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>0.4623028450989635</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>-3278.460471492119</v>
+        <v>0</v>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>0.08396376422626911</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>-261.7500480089586</v>
+        <v>0</v>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -42512,7 +42512,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42610,7 +42610,7 @@
         <v>8</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-4620.182984805399</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-693.7951958603617</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>9</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>-713.7959092967661</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>9</v>
       </c>
       <c r="J25" s="16" t="n">
-        <v>-649.7922632433995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>3</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>-424.1892292326012</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="16" t="n">
-        <v>-291.0102656423374</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>3</v>
       </c>
       <c r="J39" s="16" t="n">
-        <v>-2093.325428629065</v>
+        <v>0</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>11</v>
       </c>
       <c r="J41" s="16" t="n">
-        <v>-488.7554729391683</v>
+        <v>0</v>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="16" t="n">
-        <v>-1986.069089337367</v>
+        <v>0</v>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>18</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>-5377.112770960232</v>
+        <v>0</v>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -44865,7 +44865,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45638,7 +45638,7 @@
         <v>0.05752943128902078</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>-270.7074322570051</v>
+        <v>0</v>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>0.007488078343480818</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>-968.6855100148371</v>
+        <v>0</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>0.01237220616210536</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>-448.1121473391075</v>
+        <v>0</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>0.1333748985093365</v>
       </c>
       <c r="G51" s="16" t="n">
-        <v>-73.25617321247427</v>
+        <v>0</v>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>0.07720377301715224</v>
       </c>
       <c r="G55" s="16" t="n">
-        <v>-3952.343174073519</v>
+        <v>0</v>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -46708,7 +46708,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47446,7 +47446,7 @@
         <v>0.07258547325541587</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>-3.865904621567378</v>
+        <v>0</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>0.04085863950811535</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>-453.7964173754067</v>
+        <v>0</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -48551,7 +48551,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -49639,7 +49639,7 @@
         <v>0.02380459704513859</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>-99.56592188480941</v>
+        <v>0</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>0.0372430907252571</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>-75.4839063195496</v>
+        <v>0</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         <v>0.04421912606482368</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>-1411.866559265266</v>
+        <v>0</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>0.02691189705543784</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>-151.3914760320085</v>
+        <v>0</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>0.03051657823259954</v>
       </c>
       <c r="G51" s="16" t="n">
-        <v>-1112.059467252782</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>0.01659892533633349</v>
       </c>
       <c r="G52" s="16" t="n">
-        <v>-510.473050890078</v>
+        <v>0</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>0.00710004145634174</v>
       </c>
       <c r="G67" s="16" t="n">
-        <v>-746.7387849279967</v>
+        <v>0</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>0.01041071747144686</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>-1377.531289025224</v>
+        <v>0</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>0.02363224965867727</v>
       </c>
       <c r="G73" s="16" t="n">
-        <v>-484.9422090838634</v>
+        <v>0</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>0.01073702591622479</v>
       </c>
       <c r="G91" s="16" t="n">
-        <v>-6078.962499201431</v>
+        <v>0</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
@@ -51669,7 +51669,7 @@
         <v>0.003531671852057878</v>
       </c>
       <c r="G93" s="16" t="n">
-        <v>-20.52595606324257</v>
+        <v>0</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>0.1026081524285491</v>
       </c>
       <c r="G153" s="16" t="n">
-        <v>-42198.96923317195</v>
+        <v>0</v>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -54819,7 +54819,7 @@
         <v>0.03643457576553814</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>-1282.599648947667</v>
+        <v>0</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>0.05008163899271165</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-113.2660070603225</v>
+        <v>0</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>0.02442895034488028</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-128.2170220025336</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>0.08727681266949168</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-201.5028323776119</v>
+        <v>0</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>0.03941171187013181</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-382.7870501212582</v>
+        <v>0</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>0.01129048297985151</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>-685.6559999021479</v>
+        <v>0</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>0.01907085761704957</v>
       </c>
       <c r="J26" s="15" t="n">
-        <v>-66.88154492521852</v>
+        <v>0</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
@@ -55674,7 +55674,7 @@
         <v>0.115702313966239</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>-149.7168365959892</v>
+        <v>0</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>0.01977742805305823</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>-79.04229386913013</v>
+        <v>0</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>0.08396376422626911</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>-261.7500480089586</v>
+        <v>0</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>0.006016334148688285</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>-507.7366944505629</v>
+        <v>0</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
@@ -55899,7 +55899,7 @@
         <v>0.01984918990870637</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>-57.03533383910036</v>
+        <v>0</v>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>0.02361431407885112</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>-89.31732495232887</v>
+        <v>0</v>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>0.03882907127241005</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>-55.51427639514888</v>
+        <v>0</v>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>0.04237139830742175</v>
       </c>
       <c r="J36" s="15" t="n">
-        <v>-446.8798324295656</v>
+        <v>0</v>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
@@ -56124,7 +56124,7 @@
         <v>0.04630551633223693</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>-1166.205440776402</v>
+        <v>0</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
@@ -56169,7 +56169,7 @@
         <v>0.009910051491592171</v>
       </c>
       <c r="J38" s="15" t="n">
-        <v>-102.7846559692708</v>
+        <v>0</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>0.03179831467144308</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>-305.3274777172763</v>
+        <v>0</v>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>0.01154005212723684</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>-224.5084296408694</v>
+        <v>0</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>0.01124899660500166</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>-732.487778383177</v>
+        <v>0</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
@@ -56983,7 +56983,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -58872,7 +58872,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60871,7 +60871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -62870,7 +62870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64866,7 +64866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
